--- a/docs/legal/lawyer-review-package.xlsx
+++ b/docs/legal/lawyer-review-package.xlsx
@@ -651,7 +651,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -661,6 +661,7 @@
     <col width="34" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -675,6 +676,7 @@
         </is>
       </c>
     </row>
+    <row r="4"/>
     <row r="5">
       <c r="A5" s="7" t="n"/>
       <c r="B5" s="8" t="inlineStr">
@@ -830,6 +832,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="28" customHeight="1">
       <c r="B13" s="2" t="inlineStr">
         <is>
@@ -839,6 +842,18 @@
       <c r="C13" s="10" t="inlineStr">
         <is>
           <t>決済代行(Stripe Connect)を送金主体とする代替案は実装済みで、いつでも切替可能(コスト面の事業判断で自社振込を選好)。詳細: coin-economy-legal-review.md §7.3</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>🎁</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
+        <is>
+          <t>ギフト(投げ銭・2026-07-22実装): ユーザーAが購入コイン(balance)を消費してトーク相手Bに贈ると、Bの報酬コイン(earned_balance・換金可能)が即時に増える。原資は有償コインのみ(無償ボーナスは不可)。贈れる相手はトークでつながった相手に限定。→ 論点はQ11。</t>
         </is>
       </c>
     </row>
@@ -853,7 +868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1170,8 +1185,38 @@
       <c r="F11" s="13" t="inlineStr"/>
       <c r="G11" s="13" t="inlineStr"/>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Q11</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>ギフト(投げ銭)</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="inlineStr">
+        <is>
+          <t>高</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>ギフト(投げ銭)機能の適法性・整理。トークでつながった相手にコインを贈れ、受領者は換金可能な報酬コインとして受け取る(原資は贈り主の購入コインのみ・2026-07-22実装)。</t>
+        </is>
+      </c>
+      <c r="E12" s="6" t="inlineStr">
+        <is>
+          <t>(a)役務対価が明確でない任意のギフトを受領者が換金できる設計の可否/収納代行(Q1)で同様に扱えるか。 (b)ユーザー間の価値移転が「為替取引」に近づき資金移動業該当リスクが上がらないか(贈れる相手をトーク相手に限定)。 (c)自己の別アカウント間で往復させる換金ロンダリング対策(原資=有償のみ・本人確認・手数料300/回。追加制限の要否)。 (d)「投げ銭で人気の相手が稼げる」導線の射幸性・出会い系規制/景表法との関係、金額上限(現状10〜50,000/回)。 (e)利用規約第7条はギフト未想定。非返還性・原資・換金経路・禁止事項の整合を追記すべきか。</t>
+        </is>
+      </c>
+      <c r="F12" s="13" t="n"/>
+      <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13"/>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>記入例(書式の参考): 「結論: 収納代行として整理可能。理由: …。条件: 分別管理口座の開設と規約○条の修正が必要。」</t>
         </is>
@@ -1191,7 +1236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:C13"/>
+  <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1199,6 +1244,7 @@
     <col width="62" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -1206,6 +1252,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="7" t="n"/>
       <c r="B4" s="8" t="inlineStr">
@@ -1324,6 +1371,30 @@
       <c r="C13" s="6" t="inlineStr">
         <is>
           <t>実装仕様: キャンセル(返還ルール)・72時間自動確定</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>supabase/migrations/0016_bonus_coin_separation.sql</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>実装仕様: 有償/無償コインの分離・有償先消費(Q3・Q11-c)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>supabase/migrations/0019_gifts.sql</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>実装仕様: ギフト(投げ銭)。原資=有償コイン、受領=換金可能(Q11)</t>
         </is>
       </c>
     </row>
